--- a/data/trans_orig/IP07C16-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP07C16-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido estar al aire libre en 2007 (tasa de respuesta: 89,29%)</t>
+          <t>Menores según la frecuencia de haber podido estar al aire libre en 2007 (tasa de respuesta: 89,29%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>686</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5773</t>
+          <t>5732</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>692</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5785</t>
+          <t>5723</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>2090</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9428</t>
+          <t>9211</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>23,96%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6244</t>
+          <t>6180</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11797</t>
+          <t>11784</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>9264</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17619</t>
+          <t>17009</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>73,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17851</t>
+          <t>17207</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27309</t>
+          <t>26652</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>69,33%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5597</t>
+          <t>5717</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2866</t>
+          <t>3273</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10180</t>
+          <t>10495</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4964</t>
+          <t>5638</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13447</t>
+          <t>13957</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>36,31%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3445</t>
+          <t>2664</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4641</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>538</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4846</t>
+          <t>5680</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>14,78%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23199</t>
+          <t>23682</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32730</t>
+          <t>32817</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>77,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32595</t>
+          <t>32234</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43734</t>
+          <t>43379</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>59,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59562</t>
+          <t>59586</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>73585</t>
+          <t>73463</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>61,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>75,8%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7589</t>
+          <t>7014</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16744</t>
+          <t>16018</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10349</t>
+          <t>10613</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21328</t>
+          <t>21463</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>20563</t>
+          <t>19943</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>34994</t>
+          <t>34194</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>35,28%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>625</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5253</t>
+          <t>4494</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3237</t>
+          <t>3218</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>632</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5972</t>
+          <t>5710</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2670</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3306</t>
+          <t>3007</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8784</t>
+          <t>8836</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17750</t>
+          <t>17729</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5652</t>
+          <t>6175</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13111</t>
+          <t>13127</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>54,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17034</t>
+          <t>17109</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28719</t>
+          <t>28792</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>53,3%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5197</t>
+          <t>5817</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13877</t>
+          <t>14245</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7303</t>
+          <t>7339</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14707</t>
+          <t>14805</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14843</t>
+          <t>14921</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>26094</t>
+          <t>26267</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>48,62%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2764</t>
+          <t>2805</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10123</t>
+          <t>10152</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1237</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6796</t>
+          <t>7010</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5338</t>
+          <t>5159</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>13897</t>
+          <t>14199</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>26,29%</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4134</t>
+          <t>4169</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3154</t>
+          <t>2531</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>625</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5372</t>
+          <t>4821</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>8,92%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4577</t>
+          <t>4793</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12787</t>
+          <t>12632</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>3639</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11275</t>
+          <t>11371</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9941</t>
+          <t>10281</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>21644</t>
+          <t>21345</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,25%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>12373</t>
+          <t>12532</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>21495</t>
+          <t>21675</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>67,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>11930</t>
+          <t>12786</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>21342</t>
+          <t>21823</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>27180</t>
+          <t>27268</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>40365</t>
+          <t>40220</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>42,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>62,64%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2573</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9781</t>
+          <t>9404</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4768</t>
+          <t>4648</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12858</t>
+          <t>12532</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>8781</t>
+          <t>7931</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>19377</t>
+          <t>18651</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>29,05%</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4829</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5325</t>
+          <t>5171</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4843</t>
+          <t>4627</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>11817</t>
+          <t>11726</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>58,95%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>8611</t>
+          <t>8494</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>16295</t>
+          <t>16322</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>77,1%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>15979</t>
+          <t>15836</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>26040</t>
+          <t>26405</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>64,31%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4897</t>
+          <t>4885</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>11830</t>
+          <t>12012</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>60,39%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3480</t>
+          <t>3585</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>10659</t>
+          <t>10707</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>10506</t>
+          <t>10473</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>20963</t>
+          <t>20486</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>49,89%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>703</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6803</t>
+          <t>6585</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4237</t>
+          <t>4241</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1925</t>
+          <t>1432</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>8157</t>
+          <t>7668</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>18,67%</t>
         </is>
       </c>
     </row>
@@ -3804,7 +3804,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3627</t>
+          <t>2940</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4345</t>
+          <t>3593</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>4686</t>
+          <t>4647</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>12236</t>
+          <t>12063</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>48,81%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>3820</t>
+          <t>3235</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>10400</t>
+          <t>10695</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>9919</t>
+          <t>9676</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>20150</t>
+          <t>20372</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>38,22%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>7305</t>
+          <t>7105</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>15170</t>
+          <t>15423</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>10916</t>
+          <t>10904</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>19135</t>
+          <t>19097</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>66,93%</t>
+          <t>66,8%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>20242</t>
+          <t>19964</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>31750</t>
+          <t>31804</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>59,67%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1902</t>
+          <t>1916</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>8008</t>
+          <t>7560</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3152</t>
+          <t>3128</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>10220</t>
+          <t>9675</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>6009</t>
+          <t>5813</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>14985</t>
+          <t>14531</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>27,26%</t>
         </is>
       </c>
     </row>
@@ -4486,7 +4486,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4375</t>
+          <t>4313</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3521</t>
+          <t>4075</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>722</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>5790</t>
+          <t>6528</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>12,25%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>19211</t>
+          <t>19142</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>30958</t>
+          <t>31063</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>61,59%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>16321</t>
+          <t>16307</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>28686</t>
+          <t>28072</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>52,0%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>39513</t>
+          <t>39382</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>56545</t>
+          <t>54727</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>52,41%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>12961</t>
+          <t>13124</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>24312</t>
+          <t>24155</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>47,9%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>16584</t>
+          <t>17328</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>28840</t>
+          <t>29194</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>32537</t>
+          <t>32932</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>49179</t>
+          <t>48792</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>46,73%</t>
         </is>
       </c>
     </row>
@@ -5050,7 +5050,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2807</t>
+          <t>2792</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5065,7 +5065,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>4097</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>12752</t>
+          <t>12294</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>8327</t>
+          <t>8494</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>19553</t>
+          <t>20115</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>19,26%</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>3354</t>
+          <t>3607</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>4707</t>
+          <t>4198</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>645</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>5693</t>
+          <t>6122</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -5281,7 +5281,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>3677</t>
+          <t>4083</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -5506,12 +5506,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>20280</t>
+          <t>19761</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>34095</t>
+          <t>33742</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5521,12 +5521,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>19985</t>
+          <t>20152</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>32956</t>
+          <t>33321</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>44517</t>
+          <t>44844</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>62276</t>
+          <t>63065</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>43,77%</t>
         </is>
       </c>
     </row>
@@ -5619,12 +5619,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>28259</t>
+          <t>28328</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>42126</t>
+          <t>41800</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5634,12 +5634,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>56,4%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>27287</t>
+          <t>27601</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>40276</t>
+          <t>40565</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5669,12 +5669,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>57,99%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>58931</t>
+          <t>59125</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>78085</t>
+          <t>78256</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5704,12 +5704,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>54,32%</t>
         </is>
       </c>
     </row>
@@ -5732,12 +5732,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>6381</t>
+          <t>6561</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>16742</t>
+          <t>16841</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5747,12 +5747,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>4185</t>
+          <t>4409</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>13311</t>
+          <t>12743</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>13228</t>
+          <t>12895</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>26005</t>
+          <t>26025</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,06%</t>
         </is>
       </c>
     </row>
@@ -5850,7 +5850,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>3712</t>
+          <t>3956</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>4148</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5915,12 +5915,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>488</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>5692</t>
+          <t>5558</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -5963,7 +5963,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>4447</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>4452</t>
+          <t>3477</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6033,7 +6033,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>4486</t>
+          <t>4510</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -6188,12 +6188,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>107476</t>
+          <t>106768</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>133334</t>
+          <t>134817</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>112214</t>
+          <t>111628</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>138585</t>
+          <t>138578</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>227729</t>
+          <t>227110</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>263319</t>
+          <t>265743</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>44,56%</t>
         </is>
       </c>
     </row>
@@ -6301,12 +6301,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>107019</t>
+          <t>107171</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>132199</t>
+          <t>134159</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6316,12 +6316,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6336,12 +6336,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>122374</t>
+          <t>122234</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>149263</t>
+          <t>148911</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>238069</t>
+          <t>236164</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>272780</t>
+          <t>277010</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>46,44%</t>
         </is>
       </c>
     </row>
@@ -6414,12 +6414,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>30199</t>
+          <t>30084</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>48446</t>
+          <t>48631</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6429,12 +6429,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>32094</t>
+          <t>31900</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>50515</t>
+          <t>51044</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6484,12 +6484,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>67207</t>
+          <t>66893</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>93084</t>
+          <t>94589</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,86%</t>
         </is>
       </c>
     </row>
@@ -6527,12 +6527,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>3817</t>
+          <t>4104</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>13689</t>
+          <t>12905</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>2667</t>
+          <t>2742</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>10481</t>
+          <t>10504</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6597,12 +6597,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>8452</t>
+          <t>8693</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>21307</t>
+          <t>21547</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>5319</t>
+          <t>5307</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>3436</t>
+          <t>4194</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6695,7 +6695,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6710,12 +6710,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>683</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>6026</t>
+          <t>5936</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6730,7 +6730,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6911,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido estar al aire libre en 2012 (tasa de respuesta: 95,2%)</t>
+          <t>Menores según la frecuencia de haber podido estar al aire libre en 2012 (tasa de respuesta: 95,2%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7106,12 +7106,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12795</t>
+          <t>12274</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19647</t>
+          <t>20020</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7121,12 +7121,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>52,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7141,12 +7141,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17064</t>
+          <t>16688</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24959</t>
+          <t>24687</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7176,12 +7176,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32080</t>
+          <t>31897</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42826</t>
+          <t>42718</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>60,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>81,51%</t>
         </is>
       </c>
     </row>
@@ -7219,12 +7219,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>686</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5158</t>
+          <t>5135</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7234,12 +7234,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7254,12 +7254,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1591</t>
+          <t>1556</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7734</t>
+          <t>8035</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7269,12 +7269,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7289,12 +7289,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3167</t>
+          <t>3070</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11388</t>
+          <t>10711</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7304,12 +7304,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>20,44%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>511</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5471</t>
+          <t>5353</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1669</t>
+          <t>1806</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7893</t>
+          <t>7841</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3317</t>
+          <t>3187</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11679</t>
+          <t>10896</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>20,79%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>589</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5656</t>
+          <t>5898</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>598</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5778</t>
+          <t>6663</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>12,71%</t>
         </is>
       </c>
     </row>
@@ -7788,12 +7788,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23604</t>
+          <t>24003</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34199</t>
+          <t>34563</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>73,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32875</t>
+          <t>32374</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43270</t>
+          <t>43074</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7838,12 +7838,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>60,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>80,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59078</t>
+          <t>59982</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>74944</t>
+          <t>75062</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7873,12 +7873,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>59,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>74,93%</t>
         </is>
       </c>
     </row>
@@ -7901,12 +7901,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8952</t>
+          <t>8808</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19635</t>
+          <t>18819</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>4377</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11570</t>
+          <t>12043</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7951,12 +7951,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>15157</t>
+          <t>14501</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>28314</t>
+          <t>27920</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7986,12 +7986,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>27,87%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1351</t>
+          <t>1339</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8011</t>
+          <t>8102</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2543</t>
+          <t>2503</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10511</t>
+          <t>10872</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5646</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15767</t>
+          <t>15189</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,16%</t>
         </is>
       </c>
     </row>
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>602</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5718</t>
+          <t>5710</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>602</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6564</t>
+          <t>5773</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8330,7 +8330,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -8470,12 +8470,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9216</t>
+          <t>9160</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17031</t>
+          <t>17033</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8485,12 +8485,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>73,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8505,12 +8505,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9891</t>
+          <t>9508</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18251</t>
+          <t>18363</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8520,12 +8520,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8540,12 +8540,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21401</t>
+          <t>21227</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33624</t>
+          <t>33263</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>62,91%</t>
         </is>
       </c>
     </row>
@@ -8583,12 +8583,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4215</t>
+          <t>3616</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11409</t>
+          <t>11325</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8598,12 +8598,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8618,12 +8618,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8561</t>
+          <t>8654</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17565</t>
+          <t>17486</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8633,12 +8633,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>59,25%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14160</t>
+          <t>14344</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>26167</t>
+          <t>25718</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>48,64%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>661</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>6114</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>751</t>
+          <t>702</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6327</t>
+          <t>6375</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2714</t>
+          <t>2660</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>10375</t>
+          <t>9875</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>18,68%</t>
         </is>
       </c>
     </row>
@@ -9152,12 +9152,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13780</t>
+          <t>13495</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23964</t>
+          <t>23732</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>62,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9187,12 +9187,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12867</t>
+          <t>12616</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22341</t>
+          <t>22726</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9202,12 +9202,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>65,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>28838</t>
+          <t>29026</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>43190</t>
+          <t>43238</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9237,12 +9237,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>59,26%</t>
         </is>
       </c>
     </row>
@@ -9265,12 +9265,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>11950</t>
+          <t>11686</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>22012</t>
+          <t>22312</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9280,12 +9280,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9300,12 +9300,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>9067</t>
+          <t>9088</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>18304</t>
+          <t>18596</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9315,12 +9315,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>53,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9335,12 +9335,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>23885</t>
+          <t>23764</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>37520</t>
+          <t>37862</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9350,12 +9350,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>51,89%</t>
         </is>
       </c>
     </row>
@@ -9378,12 +9378,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>787</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5892</t>
+          <t>6601</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9393,12 +9393,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9413,12 +9413,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1415</t>
+          <t>1438</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8121</t>
+          <t>8427</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2785</t>
+          <t>3046</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>11951</t>
+          <t>11622</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>15,93%</t>
         </is>
       </c>
     </row>
@@ -9834,12 +9834,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>7494</t>
+          <t>8115</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>15425</t>
+          <t>15772</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9869,12 +9869,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>12374</t>
+          <t>12434</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>18674</t>
+          <t>18224</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>61,68%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>22034</t>
+          <t>22249</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>32846</t>
+          <t>32471</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>54,58%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>79,65%</t>
         </is>
       </c>
     </row>
@@ -9947,12 +9947,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>9779</t>
+          <t>9247</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9982,12 +9982,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>656</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>6064</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4220</t>
+          <t>4479</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>13174</t>
+          <t>13262</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,53%</t>
         </is>
       </c>
     </row>
@@ -10065,7 +10065,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5868</t>
+          <t>6368</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10080,7 +10080,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10100,7 +10100,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3248</t>
+          <t>3920</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10115,7 +10115,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>807</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7322</t>
+          <t>7052</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,3%</t>
         </is>
       </c>
     </row>
@@ -10291,7 +10291,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4479</t>
+          <t>4424</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3477</t>
+          <t>2956</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -10341,7 +10341,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -10361,7 +10361,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5088</t>
+          <t>5615</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>13,77%</t>
         </is>
       </c>
     </row>
@@ -10516,12 +10516,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>8592</t>
+          <t>8127</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>17742</t>
+          <t>17458</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -10531,12 +10531,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>60,3%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>6611</t>
+          <t>6421</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>14580</t>
+          <t>14712</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>17322</t>
+          <t>17004</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>29630</t>
+          <t>29568</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>55,54%</t>
+          <t>55,42%</t>
         </is>
       </c>
     </row>
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>9989</t>
+          <t>9611</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>18887</t>
+          <t>18899</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -10644,12 +10644,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>65,27%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -10664,12 +10664,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>8940</t>
+          <t>9014</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>17005</t>
+          <t>17531</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -10679,12 +10679,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>71,87%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10699,12 +10699,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>21761</t>
+          <t>21369</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>33998</t>
+          <t>34392</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>63,73%</t>
+          <t>64,47%</t>
         </is>
       </c>
     </row>
@@ -10747,7 +10747,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>5513</t>
+          <t>5433</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10762,7 +10762,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10782,7 +10782,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3697</t>
+          <t>3615</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>719</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>6307</t>
+          <t>6567</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>12,31%</t>
         </is>
       </c>
     </row>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>9935</t>
+          <t>10163</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>21411</t>
+          <t>21497</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -11213,12 +11213,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -11233,12 +11233,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>12604</t>
+          <t>13350</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>23797</t>
+          <t>24519</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -11248,12 +11248,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -11268,12 +11268,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>26054</t>
+          <t>26089</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>41875</t>
+          <t>41556</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -11283,12 +11283,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>39,69%</t>
         </is>
       </c>
     </row>
@@ -11311,12 +11311,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>20574</t>
+          <t>20003</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>32143</t>
+          <t>31821</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -11326,12 +11326,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>61,32%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>20026</t>
+          <t>19726</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>31616</t>
+          <t>32051</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>60,7%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -11381,12 +11381,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>42174</t>
+          <t>43913</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>60501</t>
+          <t>60285</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -11396,12 +11396,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>57,58%</t>
         </is>
       </c>
     </row>
@@ -11424,12 +11424,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>4703</t>
+          <t>4748</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>13393</t>
+          <t>14444</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -11439,12 +11439,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11459,12 +11459,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>4735</t>
+          <t>5086</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>13715</t>
+          <t>14273</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -11474,12 +11474,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -11494,12 +11494,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>11025</t>
+          <t>11330</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>24357</t>
+          <t>23867</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -11509,12 +11509,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>22,8%</t>
         </is>
       </c>
     </row>
@@ -11537,12 +11537,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>654</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>5500</t>
+          <t>5409</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -11552,39 +11552,39 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
+          <t>1,26%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>10,42%</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>10,6%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -11607,12 +11607,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>657</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>5410</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -11627,7 +11627,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -11880,12 +11880,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>20474</t>
+          <t>19884</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>33498</t>
+          <t>33422</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11895,12 +11895,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11915,12 +11915,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>17026</t>
+          <t>16735</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>29242</t>
+          <t>29484</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11930,12 +11930,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11950,12 +11950,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>40199</t>
+          <t>40222</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>59374</t>
+          <t>58841</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11965,12 +11965,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,37%</t>
         </is>
       </c>
     </row>
@@ -11993,12 +11993,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>30953</t>
+          <t>31146</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>44924</t>
+          <t>45383</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>58,25%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -12028,12 +12028,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>32297</t>
+          <t>32235</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>45832</t>
+          <t>46633</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -12043,12 +12043,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>58,63%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -12063,12 +12063,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>68157</t>
+          <t>67945</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>88072</t>
+          <t>87232</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -12078,12 +12078,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>55,4%</t>
         </is>
       </c>
     </row>
@@ -12106,12 +12106,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>8170</t>
+          <t>7715</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>18616</t>
+          <t>18505</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>10647</t>
+          <t>10501</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>21441</t>
+          <t>21840</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>21594</t>
+          <t>21234</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>36727</t>
+          <t>36548</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -12191,12 +12191,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,21%</t>
         </is>
       </c>
     </row>
@@ -12224,7 +12224,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3046</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12239,7 +12239,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -12259,7 +12259,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>4615</t>
+          <t>3946</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -12289,12 +12289,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>595</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>5345</t>
+          <t>5444</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -12309,7 +12309,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>3171</t>
+          <t>2918</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -12387,7 +12387,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -12407,7 +12407,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>2931</t>
+          <t>2914</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -12562,12 +12562,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>131633</t>
+          <t>130908</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>161209</t>
+          <t>160430</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12597,12 +12597,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>145107</t>
+          <t>140888</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>173775</t>
+          <t>171065</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -12612,12 +12612,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -12632,12 +12632,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>282303</t>
+          <t>284324</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>322660</t>
+          <t>324255</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -12647,12 +12647,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>51,09%</t>
         </is>
       </c>
     </row>
@@ -12675,12 +12675,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>109959</t>
+          <t>109008</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>137522</t>
+          <t>137725</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -12710,12 +12710,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>105097</t>
+          <t>104619</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>134851</t>
+          <t>134653</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -12725,12 +12725,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -12745,12 +12745,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>223408</t>
+          <t>222853</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>262436</t>
+          <t>263010</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -12760,12 +12760,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>41,44%</t>
         </is>
       </c>
     </row>
@@ -12788,12 +12788,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>28262</t>
+          <t>28458</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>46525</t>
+          <t>47279</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -12823,12 +12823,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>32871</t>
+          <t>33550</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>52274</t>
+          <t>52875</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -12838,12 +12838,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -12858,12 +12858,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>66040</t>
+          <t>65083</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>93579</t>
+          <t>92040</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -12873,12 +12873,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,5%</t>
         </is>
       </c>
     </row>
@@ -12901,12 +12901,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2156</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>9456</t>
+          <t>9753</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12916,12 +12916,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -12941,7 +12941,7 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>4549</t>
+          <t>4493</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -12956,7 +12956,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -12971,12 +12971,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>3221</t>
+          <t>3203</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>11626</t>
+          <t>11284</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -12986,12 +12986,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -13019,7 +13019,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>4560</t>
+          <t>4590</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -13049,12 +13049,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>1258</t>
+          <t>1192</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>7507</t>
+          <t>7109</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -13064,12 +13064,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -13084,12 +13084,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>1523</t>
+          <t>1820</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>8477</t>
+          <t>9564</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -13099,12 +13099,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -13285,7 +13285,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido estar al aire libre en 2016 (tasa de respuesta: 95,47%)</t>
+          <t>Menores según la frecuencia de haber podido estar al aire libre en 2016 (tasa de respuesta: 95,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11542</t>
+          <t>11632</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19348</t>
+          <t>19450</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13495,12 +13495,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>73,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13515,12 +13515,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7316</t>
+          <t>7348</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15043</t>
+          <t>15573</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13530,12 +13530,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13550,12 +13550,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20650</t>
+          <t>20084</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32593</t>
+          <t>32567</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13565,12 +13565,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>63,74%</t>
         </is>
       </c>
     </row>
@@ -13593,12 +13593,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4815</t>
+          <t>4974</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12172</t>
+          <t>12616</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13608,12 +13608,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13628,12 +13628,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>4323</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12401</t>
+          <t>12157</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>49,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13663,12 +13663,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11017</t>
+          <t>11224</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21842</t>
+          <t>22168</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13678,12 +13678,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>43,39%</t>
         </is>
       </c>
     </row>
@@ -13711,7 +13711,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5012</t>
+          <t>5020</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13726,7 +13726,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -13741,12 +13741,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>1835</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8540</t>
+          <t>8716</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -13756,12 +13756,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -13776,12 +13776,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2692</t>
+          <t>2863</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11305</t>
+          <t>11182</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -13791,12 +13791,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>21,88%</t>
         </is>
       </c>
     </row>
@@ -13824,7 +13824,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4692</t>
+          <t>4629</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -13839,7 +13839,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -13859,7 +13859,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4840</t>
+          <t>4412</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -13889,12 +13889,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>634</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6298</t>
+          <t>6311</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -13904,12 +13904,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,35%</t>
         </is>
       </c>
     </row>
@@ -14162,12 +14162,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19768</t>
+          <t>19773</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31913</t>
+          <t>31721</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14177,12 +14177,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>60,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14197,12 +14197,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22688</t>
+          <t>22920</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35111</t>
+          <t>35257</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14212,12 +14212,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14232,12 +14232,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>45873</t>
+          <t>45925</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>63323</t>
+          <t>63000</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14247,12 +14247,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>57,96%</t>
         </is>
       </c>
     </row>
@@ -14275,12 +14275,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14539</t>
+          <t>15185</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26248</t>
+          <t>26924</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -14290,12 +14290,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -14310,12 +14310,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16531</t>
+          <t>16550</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28482</t>
+          <t>28255</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -14325,12 +14325,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -14345,12 +14345,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>34521</t>
+          <t>34953</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>51430</t>
+          <t>52106</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -14360,12 +14360,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>47,94%</t>
         </is>
       </c>
     </row>
@@ -14388,12 +14388,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2698</t>
+          <t>2925</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10541</t>
+          <t>10356</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14403,12 +14403,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14423,12 +14423,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7010</t>
+          <t>7068</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14438,12 +14438,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5247</t>
+          <t>5073</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15047</t>
+          <t>15115</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14473,12 +14473,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,91%</t>
         </is>
       </c>
     </row>
@@ -14541,7 +14541,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6535</t>
+          <t>5841</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14556,7 +14556,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14576,7 +14576,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6110</t>
+          <t>6123</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14591,7 +14591,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9881</t>
+          <t>10327</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20134</t>
+          <t>20221</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -14859,12 +14859,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,18%</t>
+          <t>56,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -14879,12 +14879,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9410</t>
+          <t>9236</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18841</t>
+          <t>18318</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -14894,12 +14894,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>55,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -14914,12 +14914,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22178</t>
+          <t>22029</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36601</t>
+          <t>35338</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -14929,12 +14929,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>51,34%</t>
         </is>
       </c>
     </row>
@@ -14957,12 +14957,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8876</t>
+          <t>8573</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18733</t>
+          <t>18115</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -14972,12 +14972,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -14992,12 +14992,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6057</t>
+          <t>6566</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15563</t>
+          <t>15451</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15007,12 +15007,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>46,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15027,12 +15027,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>16564</t>
+          <t>17458</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>31138</t>
+          <t>30514</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15042,12 +15042,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>44,33%</t>
         </is>
       </c>
     </row>
@@ -15070,12 +15070,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4039</t>
+          <t>3929</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12293</t>
+          <t>12829</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15085,12 +15085,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15105,12 +15105,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5188</t>
+          <t>5166</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13590</t>
+          <t>14162</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15120,12 +15120,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15140,12 +15140,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11034</t>
+          <t>11062</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>23165</t>
+          <t>23148</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15155,12 +15155,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,63%</t>
         </is>
       </c>
     </row>
@@ -15526,12 +15526,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15264</t>
+          <t>15376</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24130</t>
+          <t>24436</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15541,12 +15541,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>47,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15561,12 +15561,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20852</t>
+          <t>21279</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30272</t>
+          <t>30706</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15576,12 +15576,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15596,12 +15596,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>39642</t>
+          <t>38675</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>52451</t>
+          <t>52025</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15611,12 +15611,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>55,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>74,95%</t>
         </is>
       </c>
     </row>
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3039</t>
+          <t>2904</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>9965</t>
+          <t>10163</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -15654,12 +15654,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -15674,12 +15674,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3022</t>
+          <t>2907</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10829</t>
+          <t>10630</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -15689,12 +15689,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -15709,12 +15709,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7517</t>
+          <t>7701</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>18812</t>
+          <t>18458</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -15724,12 +15724,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,59%</t>
         </is>
       </c>
     </row>
@@ -15752,12 +15752,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7994</t>
+          <t>7886</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -15767,12 +15767,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -15787,12 +15787,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>648</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6157</t>
+          <t>6159</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -15822,12 +15822,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2758</t>
+          <t>2744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>11366</t>
+          <t>11375</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -15837,12 +15837,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,39%</t>
         </is>
       </c>
     </row>
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>568</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5291</t>
+          <t>5524</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -15880,12 +15880,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -15900,12 +15900,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>634</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5142</t>
+          <t>5520</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -15915,12 +15915,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -15935,12 +15935,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1883</t>
+          <t>1584</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8280</t>
+          <t>8802</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -15950,12 +15950,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,68%</t>
         </is>
       </c>
     </row>
@@ -15983,7 +15983,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3418</t>
+          <t>3964</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -15998,7 +15998,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -16053,7 +16053,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4102</t>
+          <t>3338</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -16068,7 +16068,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -16208,12 +16208,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1874</t>
+          <t>1659</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7575</t>
+          <t>8056</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16223,12 +16223,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16243,12 +16243,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2703</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>9649</t>
+          <t>9531</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16258,12 +16258,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16278,12 +16278,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5657</t>
+          <t>5910</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>14822</t>
+          <t>14877</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16293,12 +16293,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>33,3%</t>
         </is>
       </c>
     </row>
@@ -16321,12 +16321,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6961</t>
+          <t>6733</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14398</t>
+          <t>14098</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16336,12 +16336,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16356,12 +16356,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>10818</t>
+          <t>10816</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>19151</t>
+          <t>19220</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16371,12 +16371,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>74,73%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16391,12 +16391,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>20826</t>
+          <t>20416</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>31503</t>
+          <t>31017</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16406,12 +16406,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>69,42%</t>
         </is>
       </c>
     </row>
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1821</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>7554</t>
+          <t>7942</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16449,12 +16449,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16469,12 +16469,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2051</t>
+          <t>2126</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>8600</t>
+          <t>9008</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16484,12 +16484,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16504,12 +16504,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4940</t>
+          <t>5339</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>13659</t>
+          <t>13572</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16519,12 +16519,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,37%</t>
         </is>
       </c>
     </row>
@@ -16890,12 +16890,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>7908</t>
+          <t>8007</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>17258</t>
+          <t>16880</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -16905,12 +16905,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>54,72%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -16925,12 +16925,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>9605</t>
+          <t>9616</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>19427</t>
+          <t>19673</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -16940,12 +16940,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>63,58%</t>
+          <t>64,39%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -16960,12 +16960,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>20606</t>
+          <t>20921</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>34362</t>
+          <t>34104</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -16975,12 +16975,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>55,54%</t>
         </is>
       </c>
     </row>
@@ -17003,12 +17003,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>10824</t>
+          <t>10452</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>19884</t>
+          <t>20003</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -17018,12 +17018,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -17038,12 +17038,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>7131</t>
+          <t>7226</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>16659</t>
+          <t>16551</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -17053,12 +17053,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>54,17%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -17073,12 +17073,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>20706</t>
+          <t>20351</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>34114</t>
+          <t>33687</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -17088,12 +17088,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>55,56%</t>
+          <t>54,86%</t>
         </is>
       </c>
     </row>
@@ -17121,7 +17121,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>4870</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17136,7 +17136,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17151,12 +17151,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1605</t>
+          <t>1580</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>8584</t>
+          <t>8380</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17166,12 +17166,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17186,12 +17186,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2428</t>
+          <t>2396</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>11175</t>
+          <t>11458</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17201,12 +17201,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,66%</t>
         </is>
       </c>
     </row>
@@ -17234,7 +17234,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>5821</t>
+          <t>5237</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17249,7 +17249,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>5442</t>
+          <t>5486</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17319,7 +17319,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,93%</t>
         </is>
       </c>
     </row>
@@ -17572,12 +17572,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>24587</t>
+          <t>24828</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>38101</t>
+          <t>38189</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -17587,12 +17587,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>55,85%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -17607,12 +17607,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>21905</t>
+          <t>21655</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>35140</t>
+          <t>35619</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -17622,12 +17622,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>54,91%</t>
+          <t>55,66%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -17642,12 +17642,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>50547</t>
+          <t>50097</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>69602</t>
+          <t>70187</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -17657,12 +17657,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>53,08%</t>
         </is>
       </c>
     </row>
@@ -17685,12 +17685,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>15718</t>
+          <t>15789</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>28392</t>
+          <t>28391</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -17700,7 +17700,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -17720,12 +17720,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>21677</t>
+          <t>21190</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>35404</t>
+          <t>34660</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -17735,12 +17735,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>54,16%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -17755,12 +17755,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>41119</t>
+          <t>41286</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>59565</t>
+          <t>60535</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -17770,12 +17770,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>45,78%</t>
         </is>
       </c>
     </row>
@@ -17798,12 +17798,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>8461</t>
+          <t>8104</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>19044</t>
+          <t>19149</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -17813,12 +17813,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -17833,12 +17833,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>2156</t>
+          <t>2129</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>10377</t>
+          <t>10045</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -17848,12 +17848,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -17868,12 +17868,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>12312</t>
+          <t>11811</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>26270</t>
+          <t>25229</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -17883,12 +17883,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,08%</t>
         </is>
       </c>
     </row>
@@ -17916,7 +17916,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>4645</t>
+          <t>5022</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -17931,7 +17931,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -17946,12 +17946,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>705</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>5874</t>
+          <t>5809</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -17961,12 +17961,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -17981,12 +17981,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>1342</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>7882</t>
+          <t>7953</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -17996,12 +17996,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -18029,7 +18029,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>3836</t>
+          <t>3167</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -18044,7 +18044,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -18099,7 +18099,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3552</t>
+          <t>3773</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -18114,7 +18114,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -18254,12 +18254,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>16461</t>
+          <t>16561</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>29308</t>
+          <t>30154</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -18269,12 +18269,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -18289,12 +18289,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>16170</t>
+          <t>15433</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>29215</t>
+          <t>29191</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -18304,12 +18304,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -18324,12 +18324,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>35748</t>
+          <t>35466</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>53830</t>
+          <t>54049</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -18339,12 +18339,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,61%</t>
         </is>
       </c>
     </row>
@@ -18367,12 +18367,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>34023</t>
+          <t>33622</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>47796</t>
+          <t>48327</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -18382,12 +18382,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -18402,12 +18402,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>31717</t>
+          <t>31370</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>45504</t>
+          <t>45517</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -18417,12 +18417,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -18437,12 +18437,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>69754</t>
+          <t>69120</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>89452</t>
+          <t>89962</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -18452,12 +18452,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>57,61%</t>
         </is>
       </c>
     </row>
@@ -18480,12 +18480,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>9032</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>20034</t>
+          <t>19494</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -18495,12 +18495,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -18515,12 +18515,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>10073</t>
+          <t>9540</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>21579</t>
+          <t>20842</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -18530,12 +18530,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -18550,12 +18550,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>20894</t>
+          <t>21174</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>36890</t>
+          <t>37061</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -18565,12 +18565,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,73%</t>
         </is>
       </c>
     </row>
@@ -18598,7 +18598,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>3896</t>
+          <t>3972</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -18613,7 +18613,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -18633,7 +18633,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>4257</t>
+          <t>4563</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -18648,7 +18648,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -18663,12 +18663,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>591</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>5864</t>
+          <t>5903</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -18683,7 +18683,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>4401</t>
+          <t>5058</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -18726,7 +18726,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -18781,7 +18781,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>4496</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -18796,7 +18796,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -18936,12 +18936,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>130054</t>
+          <t>132149</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>162465</t>
+          <t>162357</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -18951,12 +18951,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -18971,12 +18971,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>135332</t>
+          <t>134576</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>166544</t>
+          <t>165548</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -18986,12 +18986,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -19006,12 +19006,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>275300</t>
+          <t>274918</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>318772</t>
+          <t>318754</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -19021,7 +19021,7 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -19049,12 +19049,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>121193</t>
+          <t>122242</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>152834</t>
+          <t>152691</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -19064,12 +19064,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>124687</t>
+          <t>126125</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>155226</t>
+          <t>156471</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -19099,12 +19099,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -19119,12 +19119,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>256512</t>
+          <t>252808</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>300944</t>
+          <t>298504</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -19134,12 +19134,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>43,1%</t>
         </is>
       </c>
     </row>
@@ -19162,12 +19162,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>40773</t>
+          <t>41040</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>62383</t>
+          <t>62274</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -19177,12 +19177,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>38480</t>
+          <t>37151</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>60807</t>
+          <t>58875</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -19212,12 +19212,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -19232,12 +19232,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>84450</t>
+          <t>84793</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>114198</t>
+          <t>116119</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -19247,12 +19247,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,77%</t>
         </is>
       </c>
     </row>
@@ -19275,12 +19275,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>3506</t>
+          <t>3678</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>12760</t>
+          <t>13233</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -19290,12 +19290,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -19310,12 +19310,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>4423</t>
+          <t>4389</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>14087</t>
+          <t>14831</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -19325,12 +19325,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -19345,12 +19345,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>9683</t>
+          <t>10009</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>23195</t>
+          <t>22903</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -19360,12 +19360,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -19388,12 +19388,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>786</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>6674</t>
+          <t>6722</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -19403,12 +19403,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -19458,12 +19458,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>795</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>7122</t>
+          <t>7270</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -19478,7 +19478,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
